--- a/data/trans_orig/P2A_psíq_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>14687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>261719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272008</t>
+          <t>272018</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253762</t>
+          <t>253366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519174</t>
+          <t>519161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530973</t>
+          <t>531091</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>24278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29137</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483917</t>
+          <t>483528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480634</t>
+          <t>479671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495171</t>
+          <t>494761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>967887</t>
+          <t>968451</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>986188</t>
+          <t>986129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311541</t>
+          <t>311615</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328542</t>
+          <t>327790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643921</t>
+          <t>644218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653212</t>
+          <t>653200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>927</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347554</t>
+          <t>347502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357616</t>
+          <t>357621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363023</t>
+          <t>363414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370536</t>
+          <t>370529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>715175</t>
+          <t>714817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>726854</t>
+          <t>727247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195490</t>
+          <t>196102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198725</t>
+          <t>198806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206663</t>
+          <t>206654</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398005</t>
+          <t>397754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408581</t>
+          <t>408862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,62 +2483,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4898</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>6722</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265900</t>
+          <t>266568</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>276174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278144</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>542233</t>
+          <t>544057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,82 +2806,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>4760</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10479</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4760</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1862</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>10415</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>9372</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>16848</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>9372</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>3973</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>16164</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>604671</t>
+          <t>604581</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613259</t>
+          <t>613282</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,82 +2919,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>633459</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>627740</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>636368</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>633459</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>627804</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>636357</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1209</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1243874</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1236398</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1248527</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>99,25%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1209</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1243874</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1237082</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1249273</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15612</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>728183</t>
+          <t>728450</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>740594</t>
+          <t>740699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>766474</t>
+          <t>765888</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>779333</t>
+          <t>779305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1498988</t>
+          <t>1500612</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1517847</t>
+          <t>1517996</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19763</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>42995</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>28386</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53787</t>
+          <t>53962</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53688</t>
+          <t>54557</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87187</t>
+          <t>87362</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3234548</t>
+          <t>3233548</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3256780</t>
+          <t>3256393</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3325410</t>
+          <t>3325235</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3350575</t>
+          <t>3350811</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6568554</t>
+          <t>6568379</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6602053</t>
+          <t>6601184</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35022</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271505</t>
+          <t>271791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287857</t>
+          <t>288089</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268125</t>
+          <t>269194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282699</t>
+          <t>283040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546961</t>
+          <t>545694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568250</t>
+          <t>567471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490516</t>
+          <t>489844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503555</t>
+          <t>503285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509819</t>
+          <t>509456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520633</t>
+          <t>520693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1006134</t>
+          <t>1005183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022187</t>
+          <t>1022521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19032</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15627</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8559</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28727</t>
+          <t>27893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305014</t>
+          <t>304358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320828</t>
+          <t>320844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325393</t>
+          <t>326600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337858</t>
+          <t>337930</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636339</t>
+          <t>637173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656507</t>
+          <t>656508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19676</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25524</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363525</t>
+          <t>363614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372926</t>
+          <t>372929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369275</t>
+          <t>369260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382152</t>
+          <t>382374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737409</t>
+          <t>737989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753864</t>
+          <t>754180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198634</t>
+          <t>197710</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210294</t>
+          <t>209373</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204359</t>
+          <t>205237</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216644</t>
+          <t>216642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407783</t>
+          <t>408036</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423493</t>
+          <t>423825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20770</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262874</t>
+          <t>262662</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271991</t>
+          <t>272017</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265426</t>
+          <t>265333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276944</t>
+          <t>276948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>533242</t>
+          <t>533437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547757</t>
+          <t>547205</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>30322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>642922</t>
+          <t>643569</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>656661</t>
+          <t>656835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>677825</t>
+          <t>676612</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689792</t>
+          <t>688877</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1323940</t>
+          <t>1326319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1343839</t>
+          <t>1343647</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26114</t>
+          <t>26261</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>13545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33735</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>763979</t>
+          <t>762451</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777030</t>
+          <t>776171</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>797739</t>
+          <t>797592</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815405</t>
+          <t>815170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1569216</t>
+          <t>1568598</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1589219</t>
+          <t>1589406</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>46068</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>81624</t>
+          <t>85110</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58274</t>
+          <t>59306</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>95142</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>113673</t>
+          <t>114140</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>164089</t>
+          <t>162553</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3345155</t>
+          <t>3341669</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3380711</t>
+          <t>3377998</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3463167</t>
+          <t>3465323</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3500035</t>
+          <t>3499003</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6820999</t>
+          <t>6822535</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6871415</t>
+          <t>6870948</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>23308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278235</t>
+          <t>278322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290970</t>
+          <t>290476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274874</t>
+          <t>275028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286526</t>
+          <t>286649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558326</t>
+          <t>559156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575522</t>
+          <t>575463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495804</t>
+          <t>496238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512018</t>
+          <t>512866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521078</t>
+          <t>521119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1012302</t>
+          <t>1011141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023521</t>
+          <t>1022687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316745</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325133</t>
+          <t>326349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334548</t>
+          <t>335096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644931</t>
+          <t>645313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653813</t>
+          <t>653808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>18678</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,47 +8458,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>27044</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>17936</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>39434</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>27044</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>17137</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>40171</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351878</t>
+          <t>351286</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365332</t>
+          <t>365039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359708</t>
+          <t>360823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378123</t>
+          <t>378291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,47 +8571,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>730203</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>717813</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>739311</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>96,43%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>94,79%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>97,63%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>730203</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>717076</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>740110</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205163</t>
+          <t>204545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208346</t>
+          <t>208663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217553</t>
+          <t>217567</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>416779</t>
+          <t>417588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426940</t>
+          <t>427718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258249</t>
+          <t>257954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263746</t>
+          <t>263218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272193</t>
+          <t>272187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525996</t>
+          <t>526607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535248</t>
+          <t>535166</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646532</t>
+          <t>646634</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655509</t>
+          <t>655514</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>677844</t>
+          <t>678436</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689137</t>
+          <t>688418</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1330837</t>
+          <t>1330434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1342999</t>
+          <t>1343448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>29536</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764314</t>
+          <t>764150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775443</t>
+          <t>775457</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>804556</t>
+          <t>805621</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820618</t>
+          <t>820375</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1575255</t>
+          <t>1575214</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1593223</t>
+          <t>1593677</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>21114</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45701</t>
+          <t>46130</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43518</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74307</t>
+          <t>74139</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>70551</t>
+          <t>71741</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>109519</t>
+          <t>113052</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3348649</t>
+          <t>3348220</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3371903</t>
+          <t>3373236</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3470235</t>
+          <t>3470403</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3501024</t>
+          <t>3501659</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6829373</t>
+          <t>6825840</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6868341</t>
+          <t>6867151</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>20806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301970</t>
+          <t>302687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310332</t>
+          <t>310525</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272134</t>
+          <t>272674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286099</t>
+          <t>286042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>580854</t>
+          <t>580271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595254</t>
+          <t>594934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>26671</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>45546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493080</t>
+          <t>491719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511003</t>
+          <t>511392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489492</t>
+          <t>489408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505526</t>
+          <t>505674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>990868</t>
+          <t>987813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1014601</t>
+          <t>1014053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>22321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304278</t>
+          <t>304337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313006</t>
+          <t>312996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>336214</t>
+          <t>335945</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>344934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643839</t>
+          <t>642857</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656372</t>
+          <t>656334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>309392</t>
+          <t>309494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464012</t>
+          <t>463968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472643</t>
+          <t>472795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>775989</t>
+          <t>776337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>784537</t>
+          <t>784520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174090</t>
+          <t>174603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255906</t>
+          <t>256067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>432294</t>
+          <t>432057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437029</t>
+          <t>437023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27981</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252380</t>
+          <t>252640</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263952</t>
+          <t>264025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>243235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251181</t>
+          <t>251218</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>498711</t>
+          <t>498865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513299</t>
+          <t>513667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38168</t>
+          <t>39181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>505357</t>
+          <t>543684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64828</t>
+          <t>64011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>739421</t>
+          <t>694796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>586111</t>
+          <t>585098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609161</t>
+          <t>608719</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>343908</t>
+          <t>305581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>804872</t>
+          <t>805018</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>734123</t>
+          <t>778748</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1408716</t>
+          <t>1409533</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>38626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>906285</t>
+          <t>905072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>924098</t>
+          <t>923717</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>695694</t>
+          <t>696404</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>708082</t>
+          <t>708708</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1608782</t>
+          <t>1607826</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1629988</t>
+          <t>1629930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>55572</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96163</t>
+          <t>92622</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99266</t>
+          <t>99799</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>948285</t>
+          <t>932453</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>166849</t>
+          <t>168822</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1081122</t>
+          <t>1039504</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3363654</t>
+          <t>3367195</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3404245</t>
+          <t>3406402</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2763995</t>
+          <t>2779827</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3613014</t>
+          <t>3612481</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6090975</t>
+          <t>6132593</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7005248</t>
+          <t>7003275</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_psíq_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261719</t>
+          <t>261735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272018</t>
+          <t>272002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253366</t>
+          <t>254382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519161</t>
+          <t>518989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531091</t>
+          <t>531099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24278</t>
+          <t>24087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28573</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483528</t>
+          <t>482492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479671</t>
+          <t>479862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>494761</t>
+          <t>495360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>968451</t>
+          <t>969476</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>986129</t>
+          <t>986304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311615</t>
+          <t>312492</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327790</t>
+          <t>328696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644218</t>
+          <t>644497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653200</t>
+          <t>653206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347502</t>
+          <t>347739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357621</t>
+          <t>357103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363414</t>
+          <t>363394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370529</t>
+          <t>370543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>714817</t>
+          <t>714901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>727247</t>
+          <t>727061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196102</t>
+          <t>195824</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>202492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198806</t>
+          <t>198584</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206654</t>
+          <t>206655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397754</t>
+          <t>398073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408862</t>
+          <t>408917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266568</t>
+          <t>265280</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>544057</t>
+          <t>543053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>604581</t>
+          <t>603669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613282</t>
+          <t>613375</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>627740</t>
+          <t>627771</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>636368</t>
+          <t>636399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1236398</t>
+          <t>1237024</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1248527</t>
+          <t>1248639</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>27135</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>728450</t>
+          <t>728485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>740699</t>
+          <t>740592</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>765888</t>
+          <t>766296</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>779305</t>
+          <t>779379</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1500612</t>
+          <t>1500171</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1517996</t>
+          <t>1517435</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28386</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>55457</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>86909</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3233548</t>
+          <t>3232333</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3256393</t>
+          <t>3255988</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,82 +3605,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3258</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3339721</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3323740</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3350673</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6444</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6586525</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6568832</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6602895</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3258</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3339721</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3325235</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3350811</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6444</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6586525</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6568379</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6601184</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>14026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36289</t>
+          <t>34697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271791</t>
+          <t>272172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288089</t>
+          <t>287866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269194</t>
+          <t>268574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283040</t>
+          <t>283189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>545694</t>
+          <t>547286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567471</t>
+          <t>567957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15683</t>
+          <t>14288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14309</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24109</t>
+          <t>24878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489844</t>
+          <t>491239</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503285</t>
+          <t>503489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509456</t>
+          <t>509346</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520693</t>
+          <t>520648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005183</t>
+          <t>1004414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022521</t>
+          <t>1022032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>20733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27893</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304358</t>
+          <t>303313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320844</t>
+          <t>320798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326600</t>
+          <t>326313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337930</t>
+          <t>338369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>637173</t>
+          <t>636646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656508</t>
+          <t>656698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24944</t>
+          <t>24912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363614</t>
+          <t>363249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372929</t>
+          <t>372934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369260</t>
+          <t>369447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382374</t>
+          <t>382371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737989</t>
+          <t>738021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754180</t>
+          <t>753512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24173</t>
+          <t>24582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197710</t>
+          <t>197133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209373</t>
+          <t>209245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205237</t>
+          <t>205106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216642</t>
+          <t>216404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>408036</t>
+          <t>407627</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423825</t>
+          <t>423521</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20575</t>
+          <t>21254</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262662</t>
+          <t>263014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272017</t>
+          <t>272045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265333</t>
+          <t>266127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276948</t>
+          <t>276971</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>533437</t>
+          <t>532758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547205</t>
+          <t>547817</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>30639</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643569</t>
+          <t>643368</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>656835</t>
+          <t>656998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>676612</t>
+          <t>676913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688877</t>
+          <t>688829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1326319</t>
+          <t>1326002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1343647</t>
+          <t>1344108</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26261</t>
+          <t>27217</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34353</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762451</t>
+          <t>763416</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776171</t>
+          <t>776206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>797592</t>
+          <t>796636</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815170</t>
+          <t>815055</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1568598</t>
+          <t>1569990</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1589406</t>
+          <t>1589786</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48781</t>
+          <t>48481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>83120</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>58689</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>93319</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114140</t>
+          <t>114989</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>162553</t>
+          <t>163756</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3341669</t>
+          <t>3343659</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3377998</t>
+          <t>3378298</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3465323</t>
+          <t>3464990</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3499003</t>
+          <t>3499620</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6822535</t>
+          <t>6821332</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6870948</t>
+          <t>6870099</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23308</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278322</t>
+          <t>279210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290476</t>
+          <t>291287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275028</t>
+          <t>275362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286649</t>
+          <t>286527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559156</t>
+          <t>559704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575463</t>
+          <t>575832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496238</t>
+          <t>495521</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512866</t>
+          <t>511916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521119</t>
+          <t>521112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1011141</t>
+          <t>1012821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022687</t>
+          <t>1022737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326349</t>
+          <t>325970</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335096</t>
+          <t>335397</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645313</t>
+          <t>644765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653808</t>
+          <t>653797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26460</t>
+          <t>27848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39434</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351286</t>
+          <t>351403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365039</t>
+          <t>364630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360823</t>
+          <t>359435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378291</t>
+          <t>377451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>717813</t>
+          <t>718776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>739311</t>
+          <t>739777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204545</t>
+          <t>205351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208663</t>
+          <t>208915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217567</t>
+          <t>216769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417588</t>
+          <t>417792</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427718</t>
+          <t>427607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>919</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257954</t>
+          <t>257568</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263218</t>
+          <t>264368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272187</t>
+          <t>272196</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526607</t>
+          <t>526031</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535166</t>
+          <t>535176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646634</t>
+          <t>647563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655514</t>
+          <t>655511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678436</t>
+          <t>678540</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688418</t>
+          <t>689183</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1330434</t>
+          <t>1330308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1343448</t>
+          <t>1343151</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>21290</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29536</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764150</t>
+          <t>764191</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775457</t>
+          <t>775590</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>805621</t>
+          <t>804877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820375</t>
+          <t>820185</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1575214</t>
+          <t>1573884</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1593677</t>
+          <t>1593140</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46130</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>42859</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74139</t>
+          <t>73940</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71741</t>
+          <t>71447</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113052</t>
+          <t>109788</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3348220</t>
+          <t>3349636</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3373236</t>
+          <t>3372531</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3470403</t>
+          <t>3470602</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3501659</t>
+          <t>3501683</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6825840</t>
+          <t>6829104</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6867151</t>
+          <t>6867445</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20806</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>307994</t>
+          <t>314308</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302687</t>
+          <t>308586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310525</t>
+          <t>317169</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>281360</t>
+          <t>308292</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272674</t>
+          <t>300157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286042</t>
+          <t>312287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>589353</t>
+          <t>622600</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>580271</t>
+          <t>614075</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594934</t>
+          <t>628374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25561</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>32412</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45546</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>504444</t>
+          <t>516427</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491719</t>
+          <t>505274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511392</t>
+          <t>524054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>499420</t>
+          <t>528302</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489408</t>
+          <t>516282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505674</t>
+          <t>534517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1003864</t>
+          <t>1044729</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>987813</t>
+          <t>1030089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1014053</t>
+          <t>1055835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22321</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>309551</t>
+          <t>308179</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304337</t>
+          <t>301191</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312996</t>
+          <t>312628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>341294</t>
+          <t>348594</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>335945</t>
+          <t>342799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>344934</t>
+          <t>352171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>650845</t>
+          <t>656774</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642857</t>
+          <t>647998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656334</t>
+          <t>662079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -11839,27 +11839,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>311842</t>
+          <t>371367</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>309494</t>
+          <t>366255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>469188</t>
+          <t>415180</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463968</t>
+          <t>408899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472795</t>
+          <t>417864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>781029</t>
+          <t>786548</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>776337</t>
+          <t>780855</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>784520</t>
+          <t>790609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>903</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -12182,27 +12182,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177379</t>
+          <t>204141</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174603</t>
+          <t>200557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>258185</t>
+          <t>228015</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>256067</t>
+          <t>226062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>435564</t>
+          <t>432155</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>432057</t>
+          <t>428222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437023</t>
+          <t>433814</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,22 +12447,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19815</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>259511</t>
+          <t>260935</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252640</t>
+          <t>254096</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264025</t>
+          <t>265606</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,27 +12560,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>247670</t>
+          <t>253707</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243235</t>
+          <t>248720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251218</t>
+          <t>257775</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>507182</t>
+          <t>514642</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>498865</t>
+          <t>506103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513667</t>
+          <t>520143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39181</t>
+          <t>40002</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>241646</t>
+          <t>46388</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>35639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>543684</t>
+          <t>62210</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>265716</t>
+          <t>71975</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64011</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>694796</t>
+          <t>91775</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>600209</t>
+          <t>694100</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585098</t>
+          <t>679685</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>608719</t>
+          <t>703480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>607619</t>
+          <t>725669</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>305581</t>
+          <t>709847</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>805018</t>
+          <t>736418</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1207828</t>
+          <t>1419769</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>778748</t>
+          <t>1399969</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1409533</t>
+          <t>1434304</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>23988</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>32162</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>23430</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>45852</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>915902</t>
+          <t>782208</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>905072</t>
+          <t>773039</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923717</t>
+          <t>788490</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>703316</t>
+          <t>815033</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696404</t>
+          <t>807343</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>708708</t>
+          <t>820746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1619219</t>
+          <t>1597241</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1607826</t>
+          <t>1583551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1629930</t>
+          <t>1605973</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53415</t>
+          <t>64472</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92622</t>
+          <t>102248</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,67 +13476,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>304229</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99799</t>
+          <t>97053</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>932453</t>
+          <t>135221</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>195258</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>170301</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>223138</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>377213</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>168822</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>1039504</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3386832</t>
+          <t>3451664</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3367195</t>
+          <t>3430514</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3406402</t>
+          <t>3468290</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,67 +13589,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3408051</t>
+          <t>3622794</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2779827</t>
+          <t>3601733</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3612481</t>
+          <t>3639901</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>7074458</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>7046578</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>7099415</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>97,31%</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>8501</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6794884</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6132593</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>7003275</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_psíq_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
